--- a/Data_Table/업적 테이블.xlsx
+++ b/Data_Table/업적 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1867,6 +1867,45 @@
       <c r="I36" s="1" t="inlineStr">
         <is>
           <t>회전회오리!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>40035</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Rat It Go!</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>30035</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>AchvIcons/ach_40035</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>렛잇고</t>
         </is>
       </c>
     </row>

--- a/Data_Table/업적 테이블.xlsx
+++ b/Data_Table/업적 테이블.xlsx
@@ -422,12 +422,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -455,35 +455,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>업적 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>설명 키</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>조건 타입</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>대상 id</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>필요 횟수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>정렬</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -502,35 +512,45 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>achv_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>achv_desc</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>achv_desc_sk</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>cond_type</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>need</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>achv_icon</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>sort_order</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -549,35 +569,45 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -592,31 +622,37 @@
           <t>반동은 계산 안 했다</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C4" s="1" t="n">
+        <v>3640001</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>30001</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40001</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>슈퍼 노바 빔</t>
         </is>
@@ -631,31 +667,37 @@
           <t>기본이야, 왓슨</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C5" s="1" t="n">
+        <v>3640002</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>30002</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40002</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>마인드 팰리스</t>
         </is>
@@ -670,31 +712,37 @@
           <t>감염자 0 → 전원</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C6" s="1" t="n">
+        <v>3640003</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>30003</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40003</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>좀비 아포칼립스</t>
         </is>
@@ -709,31 +757,37 @@
           <t>지구 뚫기</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C7" s="1" t="n">
+        <v>3640004</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>30004</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40004</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>백조의 호수(지하)</t>
         </is>
@@ -748,31 +802,37 @@
           <t>무중력은 공짜</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C8" s="1" t="n">
+        <v>3640005</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>30005</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40005</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="K8" s="1" t="inlineStr">
         <is>
           <t>무중력 구간</t>
         </is>
@@ -787,31 +847,37 @@
           <t>치즈 퐁듀 대참사</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C9" s="1" t="n">
+        <v>3640006</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E9" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>30006</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40006</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="K9" s="1" t="inlineStr">
         <is>
           <t>드래곤 퐁듀</t>
         </is>
@@ -826,31 +892,37 @@
           <t>빙의 대소동</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C10" s="1" t="n">
+        <v>3640007</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E10" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>30007</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40007</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>폴터가이스트</t>
         </is>
@@ -865,31 +937,37 @@
           <t>레밍즈</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C11" s="1" t="n">
+        <v>3640008</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>30008</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40008</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="J11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>천국의 계단</t>
         </is>
@@ -904,31 +982,37 @@
           <t>셀프 멸종</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C12" s="1" t="n">
+        <v>3640009</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>30009</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40009</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="J12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>대멸종</t>
         </is>
@@ -943,31 +1027,37 @@
           <t>인디아나 치즈</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C13" s="1" t="n">
+        <v>3640010</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E13" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>30010</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40010</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>아마겟돈(치즈)</t>
         </is>
@@ -982,31 +1072,37 @@
           <t>이미 부서져 있었다</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C14" s="1" t="n">
+        <v>3640011</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E14" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>30011</v>
       </c>
-      <c r="F14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="H14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40011</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="J14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>천본앵 난무</t>
         </is>
@@ -1021,31 +1117,37 @@
           <t>모싱 피트</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C15" s="1" t="n">
+        <v>3640012</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E15" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>30012</v>
       </c>
-      <c r="F15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="H15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40012</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="J15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="K15" s="1" t="inlineStr">
         <is>
           <t>앵콜 대폭발</t>
         </is>
@@ -1060,31 +1162,37 @@
           <t>박쥐 운전면허 탈락</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C16" s="1" t="n">
+        <v>3640013</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E16" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>30013</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="H16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40013</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="J16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="K16" s="1" t="inlineStr">
         <is>
           <t>블러드 문 변신</t>
         </is>
@@ -1099,31 +1207,37 @@
           <t>루돌프 코가 빨간 이유</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C17" s="1" t="n">
+        <v>3640014</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E17" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>30014</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="H17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40014</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="J17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>선물 대폭격</t>
         </is>
@@ -1138,31 +1252,37 @@
           <t>구석에서 킥킥</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C18" s="1" t="n">
+        <v>3640015</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E18" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>30015</v>
       </c>
-      <c r="F18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40015</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="J18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>역병 대방출</t>
         </is>
@@ -1177,31 +1297,37 @@
           <t>실존하는 공포, 쥐왕</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C19" s="1" t="n">
+        <v>3640016</v>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E19" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>30016</v>
       </c>
-      <c r="F19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="H19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40016</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="J19" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="K19" s="1" t="inlineStr">
         <is>
           <t>쥐왕 대결속</t>
         </is>
@@ -1216,31 +1342,37 @@
           <t>줄 서세요 (강제)</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C20" s="1" t="n">
+        <v>3640017</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E20" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>30017</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="H20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40017</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="J20" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>여왕 폐하의 근위대</t>
         </is>
@@ -1255,31 +1387,37 @@
           <t>인간 대포(쥐)</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C21" s="1" t="n">
+        <v>3640018</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E21" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>30018</v>
       </c>
-      <c r="F21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40018</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="J21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="K21" s="1" t="inlineStr">
         <is>
           <t>발할라 투석기</t>
         </is>
@@ -1294,31 +1432,37 @@
           <t>무면허 변신</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C22" s="1" t="n">
+        <v>3640019</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E22" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>30019</v>
       </c>
-      <c r="F22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40019</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="J22" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="K22" s="1" t="inlineStr">
         <is>
           <t>트랜스폼</t>
         </is>
@@ -1333,31 +1477,37 @@
           <t>우주.exe 재시작</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C23" s="1" t="n">
+        <v>3640020</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E23" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>30020</v>
       </c>
-      <c r="F23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40020</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="J23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="K23" s="1" t="inlineStr">
         <is>
           <t>빅뱅.exe</t>
         </is>
@@ -1372,31 +1522,37 @@
           <t>감전 주의 (진짜로)</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C24" s="1" t="n">
+        <v>3640021</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E24" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>30021</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40021</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="J24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="K24" s="1" t="inlineStr">
         <is>
           <t>건전지 과충전 대방전</t>
         </is>
@@ -1411,31 +1567,37 @@
           <t>저작권은 소중하니까요</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C25" s="1" t="n">
+        <v>3640022</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E25" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>30022</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40022</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="J25" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="K25" s="1" t="inlineStr">
         <is>
           <t>쥐랜드 성 대개장</t>
         </is>
@@ -1450,31 +1612,37 @@
           <t>불꽃놀이는 안전하게(안 함)</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C26" s="1" t="n">
+        <v>3640023</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E26" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>30023</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="H26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40023</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="J26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="K26" s="1" t="inlineStr">
         <is>
           <t>황제의 대축제</t>
         </is>
@@ -1489,31 +1657,37 @@
           <t>피라미드 팽이 챔피언</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C27" s="1" t="n">
+        <v>3640024</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E27" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>30024</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="H27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40024</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="J27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="K27" s="1" t="inlineStr">
         <is>
           <t>파라오의 피라미드</t>
         </is>
@@ -1528,31 +1702,37 @@
           <t>돌도 검이다</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C28" s="1" t="n">
+        <v>3640025</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E28" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>30025</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="H28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40025</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="J28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="K28" s="1" t="inlineStr">
         <is>
           <t>엑스칼리버</t>
         </is>
@@ -1567,31 +1747,37 @@
           <t>소원은 신중하게</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C29" s="1" t="n">
+        <v>3640026</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E29" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>30026</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="H29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40026</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="J29" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="K29" s="1" t="inlineStr">
         <is>
           <t>램프의 지니</t>
         </is>
@@ -1606,31 +1792,37 @@
           <t>표본 채집 완료</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C30" s="1" t="n">
+        <v>3640027</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E30" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>30027</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="H30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40027</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="J30" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="K30" s="1" t="inlineStr">
         <is>
           <t>UFO 대납치</t>
         </is>
@@ -1645,31 +1837,37 @@
           <t>치즈 1000개에 쥐커드</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C31" s="1" t="n">
+        <v>3640028</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E31" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>30028</v>
       </c>
-      <c r="F31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="H31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40028</t>
         </is>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="J31" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I31" s="1" t="inlineStr">
+      <c r="K31" s="1" t="inlineStr">
         <is>
           <t>쥐커드 제노사이드</t>
         </is>
@@ -1684,31 +1882,37 @@
           <t>찌리찌리찌리찌리</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C32" s="1" t="n">
+        <v>3640029</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E32" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>30029</v>
       </c>
-      <c r="F32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="H32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40029</t>
         </is>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="J32" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="I32" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>각성!! 람쥐썬더!!</t>
         </is>
@@ -1723,31 +1927,37 @@
           <t>갑분싸 뒤 뻔뻔한 인사</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C33" s="1" t="n">
+        <v>3640030</v>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E33" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>30030</v>
       </c>
-      <c r="F33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="H33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40030</t>
         </is>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="J33" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="K33" s="1" t="inlineStr">
         <is>
           <t>줴리 감사합니다</t>
         </is>
@@ -1762,31 +1972,37 @@
           <t>별 셋 (폭발 포함)</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C34" s="1" t="n">
+        <v>3640031</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>30031</v>
       </c>
-      <c r="F34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="H34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40031</t>
         </is>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="J34" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="I34" s="1" t="inlineStr">
+      <c r="K34" s="1" t="inlineStr">
         <is>
           <t>대왕 치즈 요리</t>
         </is>
@@ -1801,31 +2017,37 @@
           <t>범인은 제일 강한 놈</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C35" s="1" t="n">
+        <v>3640032</v>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>30032</v>
       </c>
-      <c r="F35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="H35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40032</t>
         </is>
       </c>
-      <c r="H35" s="1" t="n">
+      <c r="J35" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="I35" s="1" t="inlineStr">
+      <c r="K35" s="1" t="inlineStr">
         <is>
           <t>축구공 킥</t>
         </is>
@@ -1840,31 +2062,37 @@
           <t>치즈와 원만히 해결하시길</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C36" s="1" t="n">
+        <v>3640033</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="n">
         <v>30033</v>
       </c>
-      <c r="F36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="H36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40033</t>
         </is>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="J36" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="I36" s="1" t="inlineStr">
+      <c r="K36" s="1" t="inlineStr">
         <is>
           <t>회전회오리!</t>
         </is>
@@ -1879,31 +2107,37 @@
           <t>Rat It Go!</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
+      <c r="C37" s="1" t="n">
+        <v>3640035</v>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>Ult_Use</t>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>30035</v>
       </c>
-      <c r="F37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="H37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
         <is>
           <t>AchvIcons/ach_40035</t>
         </is>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="J37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="I37" s="1" t="inlineStr">
+      <c r="K37" s="1" t="inlineStr">
         <is>
           <t>렛잇고</t>
         </is>

--- a/Data_Table/업적 테이블.xlsx
+++ b/Data_Table/업적 테이블.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Achievement" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Achv_Cond_Type" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achv_Cond_Type" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Data_Table/업적 테이블.xlsx
+++ b/Data_Table/업적 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2140,6 +2140,51 @@
       <c r="K37" s="1" t="inlineStr">
         <is>
           <t>렛잇고</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>40036</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>그리고 시간은 움직인다</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>3640036</v>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>{ult} 필살기를 끝까지 쓰기</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>3740001</v>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Use</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>30036</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>AchvIcons/ach_40036</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>살인 인형</t>
         </is>
       </c>
     </row>

--- a/Data_Table/업적 테이블.xlsx
+++ b/Data_Table/업적 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2140,51 +2140,6 @@
       <c r="K37" s="1" t="inlineStr">
         <is>
           <t>렛잇고</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>40036</v>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>그리고 시간은 움직인다</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>3640036</v>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>{ult} 필살기를 끝까지 쓰기</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>3740001</v>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>Ult_Use</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>30036</v>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>AchvIcons/ach_40036</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>살인 인형</t>
         </is>
       </c>
     </row>
